--- a/data/trans_dic/P15D$nada-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P15D$nada-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no tuvo consecuencias el último accidente</t>
+          <t>Población que no tuvo consecuencias el último accidente (tasa de respuesta: 89,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,9; 34,49</t>
+          <t>7,06; 33,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13,22; 34,46</t>
+          <t>12,61; 32,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,21; 39,79</t>
+          <t>11,83; 37,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,49</t>
+          <t>0,0; 52,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,84; 48,41</t>
+          <t>15,78; 46,4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,3</t>
+          <t>0,0; 26,98</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,61</t>
+          <t>0,0; 55,86</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,3; 31,58</t>
+          <t>9,51; 33,99</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16,12; 33,5</t>
+          <t>16,58; 33,18</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8,71; 30,52</t>
+          <t>8,27; 29,59</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,41</t>
+          <t>0,0; 37,32</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>17,11; 47,21</t>
+          <t>17,06; 49,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15,21; 34,3</t>
+          <t>14,83; 34,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,63; 27,42</t>
+          <t>7,84; 28,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,32; 57,04</t>
+          <t>6,94; 56,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,26; 45,61</t>
+          <t>5,3; 45,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,45; 46,1</t>
+          <t>15,5; 46,05</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,72; 45,0</t>
+          <t>8,82; 45,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,7</t>
+          <t>0,0; 40,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17,64; 42,36</t>
+          <t>17,79; 42,3</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17,85; 34,6</t>
+          <t>17,74; 34,45</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,85; 27,48</t>
+          <t>10,28; 27,96</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,56; 41,58</t>
+          <t>8,09; 42,16</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,03; 58,57</t>
+          <t>9,7; 60,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,28; 40,0</t>
+          <t>14,12; 39,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,98</t>
+          <t>0,0; 25,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,41</t>
+          <t>0,0; 25,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,11</t>
+          <t>0,0; 42,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,48; 47,56</t>
+          <t>12,69; 47,27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,75; 34,22</t>
+          <t>3,92; 33,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,93; 23,93</t>
+          <t>3,69; 23,9</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,94; 41,28</t>
+          <t>9,79; 41,21</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15,83; 35,51</t>
+          <t>16,73; 35,77</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,3; 21,12</t>
+          <t>4,63; 20,54</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,62; 18,05</t>
+          <t>3,29; 16,76</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,35; 57,65</t>
+          <t>15,17; 57,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,56; 37,13</t>
+          <t>10,59; 37,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,65; 32,55</t>
+          <t>3,46; 30,5</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,6; 31,33</t>
+          <t>8,66; 30,97</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,21; 71,83</t>
+          <t>10,23; 77,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,78; 44,34</t>
+          <t>10,51; 41,74</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,7</t>
+          <t>0,0; 21,19</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16,39; 40,76</t>
+          <t>15,59; 41,07</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>17,22; 54,86</t>
+          <t>17,46; 54,11</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14,26; 36,02</t>
+          <t>14,67; 35,32</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,75; 19,15</t>
+          <t>3,66; 21,43</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,85; 29,74</t>
+          <t>13,42; 29,22</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,78; 74,74</t>
+          <t>8,81; 75,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,52; 56,16</t>
+          <t>7,49; 48,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,17</t>
+          <t>0,0; 46,76</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,51; 29,49</t>
+          <t>5,31; 30,93</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,79</t>
+          <t>0,0; 40,42</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,53; 44,9</t>
+          <t>15,8; 45,76</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,44; 36,12</t>
+          <t>6,85; 36,55</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,72; 20,69</t>
+          <t>4,51; 20,28</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,84; 45,73</t>
+          <t>8,92; 46,23</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16,5; 41,15</t>
+          <t>16,23; 41,48</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7,22; 30,91</t>
+          <t>7,37; 30,52</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,16; 19,5</t>
+          <t>6,27; 20,34</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 82,08</t>
+          <t>0,0; 82,61</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>23,21; 73,9</t>
+          <t>22,07; 68,86</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,14</t>
+          <t>0,0; 36,65</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15,82; 51,64</t>
+          <t>14,96; 53,5</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8,97; 61,21</t>
+          <t>8,98; 67,52</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15,54; 50,57</t>
+          <t>15,64; 53,23</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,68; 43,52</t>
+          <t>10,78; 43,0</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>16,35; 38,17</t>
+          <t>16,33; 37,52</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6,34; 53,85</t>
+          <t>12,19; 54,23</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>23,36; 52,85</t>
+          <t>23,42; 53,11</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9,96; 36,08</t>
+          <t>9,78; 33,99</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>19,43; 37,56</t>
+          <t>17,93; 36,88</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,37; 47,08</t>
+          <t>12,1; 47,59</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,49; 50,8</t>
+          <t>10,37; 49,47</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13,66; 42,42</t>
+          <t>13,44; 41,44</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,13</t>
+          <t>0,0; 20,3</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,67; 42,42</t>
+          <t>17,7; 40,63</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,09; 23,52</t>
+          <t>3,15; 25,72</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>16,52; 32,92</t>
+          <t>17,16; 33,89</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,86</t>
+          <t>0,0; 18,95</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19,41; 39,18</t>
+          <t>18,27; 39,38</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6,99; 26,24</t>
+          <t>6,15; 25,48</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>18,55; 31,92</t>
+          <t>18,51; 32,88</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>19,7; 36,19</t>
+          <t>18,6; 34,57</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>20,5; 30,95</t>
+          <t>19,99; 30,72</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11,06; 22,02</t>
+          <t>11,44; 22,29</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11,56; 23,56</t>
+          <t>11,69; 23,0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>10,23; 24,85</t>
+          <t>9,93; 25,17</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,3; 34,01</t>
+          <t>22,37; 34,44</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,28; 20,55</t>
+          <t>9,48; 20,02</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>15,21; 24,68</t>
+          <t>15,48; 24,77</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>17,24; 28,3</t>
+          <t>16,9; 28,12</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>23,1; 30,95</t>
+          <t>22,83; 30,25</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11,93; 19,28</t>
+          <t>11,93; 19,08</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>14,66; 22,03</t>
+          <t>14,81; 22,01</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no tuvo consecuencias el último accidente</t>
+          <t>Población que no tuvo consecuencias el último accidente (tasa de respuesta: 89,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2664; 11627</t>
+          <t>2381; 11398</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7880; 20551</t>
+          <t>7521; 19664</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4930; 17499</t>
+          <t>5204; 16554</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3971</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4816</t>
+          <t>0; 5553</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4857; 14844</t>
+          <t>4839; 14227</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4986</t>
+          <t>0; 4927</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 11679</t>
+          <t>0; 11133</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3678; 13992</t>
+          <t>4213; 15059</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14555; 30251</t>
+          <t>14970; 29962</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5424; 18995</t>
+          <t>5146; 18419</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 12660</t>
+          <t>0; 14577</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5978; 16494</t>
+          <t>5960; 17280</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12523; 28237</t>
+          <t>12208; 28688</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3879; 13944</t>
+          <t>3985; 14479</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1724; 15553</t>
+          <t>1893; 15360</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>975; 8463</t>
+          <t>983; 8363</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5875; 17531</t>
+          <t>5893; 17511</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1978; 10206</t>
+          <t>2001; 10206</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 6694</t>
+          <t>0; 5990</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9438; 22658</t>
+          <t>9518; 22624</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>21477; 41646</t>
+          <t>21353; 41465</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7242; 20205</t>
+          <t>7560; 20562</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3195; 17563</t>
+          <t>3418; 17810</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1049; 8745</t>
+          <t>1449; 9067</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7627; 21361</t>
+          <t>7544; 20986</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 7882</t>
+          <t>0; 9319</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 7552</t>
+          <t>0; 9352</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 6051</t>
+          <t>0; 5683</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3079; 13978</t>
+          <t>3729; 13892</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>939; 8571</t>
+          <t>982; 8453</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1101; 6707</t>
+          <t>1035; 6701</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1966; 11701</t>
+          <t>2777; 11681</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13105; 29399</t>
+          <t>13854; 29616</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2621; 12861</t>
+          <t>2818; 12510</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2352; 11738</t>
+          <t>2142; 10900</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2218; 11264</t>
+          <t>2963; 11200</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3819; 13428</t>
+          <t>3830; 13406</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1051; 9384</t>
+          <t>999; 8795</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4358; 15884</t>
+          <t>4392; 15701</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>890; 6942</t>
+          <t>989; 7447</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4121; 15513</t>
+          <t>3676; 14602</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 5558</t>
+          <t>0; 5188</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4817; 11977</t>
+          <t>4582; 12068</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5029; 16020</t>
+          <t>5099; 15801</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10145; 25624</t>
+          <t>10435; 25128</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1998; 10213</t>
+          <t>1951; 11427</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10292; 23820</t>
+          <t>10750; 23398</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>822; 7004</t>
+          <t>826; 7040</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>972; 7256</t>
+          <t>968; 6276</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 6599</t>
+          <t>0; 6541</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1595; 8533</t>
+          <t>1537; 8948</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 3928</t>
+          <t>0; 3990</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6484; 18750</t>
+          <t>6599; 19107</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1955; 10966</t>
+          <t>2080; 11095</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1316; 7321</t>
+          <t>1596; 7175</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1702; 8800</t>
+          <t>1716; 8895</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>9024; 22501</t>
+          <t>8875; 22683</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3202; 13709</t>
+          <t>3270; 13535</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3965; 12543</t>
+          <t>4034; 13082</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 3819</t>
+          <t>0; 3844</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4015; 12783</t>
+          <t>3818; 11912</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 3951</t>
+          <t>0; 4006</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2576; 8410</t>
+          <t>2437; 8712</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>818; 5579</t>
+          <t>818; 6154</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3935; 12810</t>
+          <t>3961; 13485</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3129; 12751</t>
+          <t>3159; 12601</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5388; 12575</t>
+          <t>5381; 12361</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>873; 7414</t>
+          <t>1679; 7466</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9958; 22531</t>
+          <t>9986; 22641</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4006; 14515</t>
+          <t>3935; 13675</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>9563; 18492</t>
+          <t>8828; 18154</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 1567</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2064; 10374</t>
+          <t>2666; 10485</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1440; 7714</t>
+          <t>1574; 7512</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2832; 8796</t>
+          <t>2788; 8594</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 6356</t>
+          <t>0; 4589</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9576; 22987</t>
+          <t>9593; 22017</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1240; 9440</t>
+          <t>1263; 10323</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>8745; 17431</t>
+          <t>9086; 17946</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 5381</t>
+          <t>0; 5406</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>14796; 29862</t>
+          <t>13924; 30015</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3867; 14517</t>
+          <t>3402; 14095</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>13666; 23520</t>
+          <t>13640; 24227</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>24250; 44542</t>
+          <t>22894; 42545</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>58173; 87817</t>
+          <t>56722; 87176</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>22072; 43968</t>
+          <t>22845; 44501</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>23136; 47135</t>
+          <t>23395; 46013</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>9594; 23310</t>
+          <t>9318; 23607</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>56707; 86513</t>
+          <t>56893; 87597</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>17651; 39101</t>
+          <t>18046; 38099</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>32488; 52725</t>
+          <t>33063; 52911</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>37386; 61372</t>
+          <t>36652; 60982</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>124316; 166554</t>
+          <t>122858; 162758</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>46506; 75176</t>
+          <t>46519; 74381</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>60643; 91146</t>
+          <t>61252; 91050</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P15D$nada-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P15D$nada-Edad-trans_dic.xlsx
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>8,58%</t>
         </is>
       </c>
     </row>
@@ -717,17 +717,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,06; 33,81</t>
+          <t>7,36; 35,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,61; 32,98</t>
+          <t>12,47; 33,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,83; 37,64</t>
+          <t>11,63; 38,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -737,42 +737,42 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,45</t>
+          <t>0,0; 53,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,78; 46,4</t>
+          <t>15,75; 45,67</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,98</t>
+          <t>0,0; 21,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,86</t>
+          <t>0,0; 49,36</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9,51; 33,99</t>
+          <t>9,57; 33,52</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16,58; 33,18</t>
+          <t>16,2; 33,61</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8,27; 29,59</t>
+          <t>8,44; 29,21</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,32</t>
+          <t>0,0; 30,84</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>17,65%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>17,06; 49,46</t>
+          <t>17,76; 49,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,83; 34,85</t>
+          <t>14,87; 34,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,84; 28,47</t>
+          <t>7,72; 27,35</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,94; 56,33</t>
+          <t>6,82; 48,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,3; 45,08</t>
+          <t>5,22; 44,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,5; 46,05</t>
+          <t>16,36; 46,84</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,82; 45,0</t>
+          <t>4,92; 45,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,0</t>
+          <t>0,0; 49,82</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17,79; 42,3</t>
+          <t>16,86; 41,88</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17,74; 34,45</t>
+          <t>17,86; 34,1</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10,28; 27,96</t>
+          <t>9,53; 27,22</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,09; 42,16</t>
+          <t>5,86; 36,33</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>7,75%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,7; 60,73</t>
+          <t>6,6; 55,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,12; 39,29</t>
+          <t>13,3; 37,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,99</t>
+          <t>0,0; 22,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,27</t>
+          <t>0,0; 18,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,36</t>
+          <t>0,0; 39,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,69; 47,27</t>
+          <t>12,94; 47,15</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,92; 33,75</t>
+          <t>3,92; 34,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,69; 23,9</t>
+          <t>3,65; 22,29</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,79; 41,21</t>
+          <t>10,32; 42,98</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16,73; 35,77</t>
+          <t>17,39; 37,17</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,63; 20,54</t>
+          <t>4,31; 22,17</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,29; 16,76</t>
+          <t>3,06; 15,48</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>19,28%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15,17; 57,32</t>
+          <t>15,42; 59,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,59; 37,07</t>
+          <t>10,61; 36,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,46; 30,5</t>
+          <t>3,71; 32,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,66; 30,97</t>
+          <t>7,73; 27,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,23; 77,05</t>
+          <t>9,17; 72,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,51; 41,74</t>
+          <t>12,18; 43,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,19</t>
+          <t>0,0; 21,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15,59; 41,07</t>
+          <t>15,6; 39,68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>17,46; 54,11</t>
+          <t>17,18; 54,66</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14,67; 35,32</t>
+          <t>14,24; 34,52</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,66; 21,43</t>
+          <t>3,7; 20,59</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13,42; 29,22</t>
+          <t>12,37; 28,32</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>11,36%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,81; 75,12</t>
+          <t>9,41; 74,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,49; 48,57</t>
+          <t>7,55; 56,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,76</t>
+          <t>0,0; 47,26</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,31; 30,93</t>
+          <t>4,63; 27,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,42</t>
+          <t>0,0; 39,41</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,8; 45,76</t>
+          <t>15,99; 45,7</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,85; 36,55</t>
+          <t>6,79; 36,57</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,51; 20,28</t>
+          <t>4,13; 19,56</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,92; 46,23</t>
+          <t>8,88; 46,44</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16,23; 41,48</t>
+          <t>15,49; 41,12</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7,37; 30,52</t>
+          <t>7,35; 31,82</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,27; 20,34</t>
+          <t>5,64; 18,23</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,14%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 82,61</t>
+          <t>0,0; 81,13</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>22,07; 68,86</t>
+          <t>21,72; 68,71</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,65</t>
+          <t>0,0; 36,67</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>14,96; 53,5</t>
+          <t>14,88; 50,51</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8,98; 67,52</t>
+          <t>9,09; 59,4</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15,64; 53,23</t>
+          <t>15,61; 50,39</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,78; 43,0</t>
+          <t>10,54; 43,63</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>16,33; 37,52</t>
+          <t>16,1; 35,51</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>12,19; 54,23</t>
+          <t>6,4; 54,2</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>23,42; 53,11</t>
+          <t>23,97; 53,41</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9,78; 33,99</t>
+          <t>9,89; 36,71</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>17,93; 36,88</t>
+          <t>18,39; 36,52</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>24,32%</t>
         </is>
       </c>
     </row>
@@ -1562,57 +1562,57 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12,1; 47,59</t>
+          <t>13,51; 51,69</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10,37; 49,47</t>
+          <t>10,19; 48,68</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13,44; 41,44</t>
+          <t>14,04; 41,54</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,3</t>
+          <t>0,0; 21,93</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,7; 40,63</t>
+          <t>16,31; 42,0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,15; 25,72</t>
+          <t>3,11; 26,18</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>17,16; 33,89</t>
+          <t>16,27; 31,67</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,95</t>
+          <t>0,0; 19,03</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18,27; 39,38</t>
+          <t>18,17; 39,58</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6,15; 25,48</t>
+          <t>5,98; 27,31</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>18,51; 32,88</t>
+          <t>18,29; 31,98</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>16,94%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>18,6; 34,57</t>
+          <t>18,72; 34,58</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>19,99; 30,72</t>
+          <t>19,97; 30,39</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11,44; 22,29</t>
+          <t>11,67; 22,43</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11,69; 23,0</t>
+          <t>11,09; 21,2</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>9,93; 25,17</t>
+          <t>10,6; 25,71</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,37; 34,44</t>
+          <t>22,94; 34,6</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,48; 20,02</t>
+          <t>9,54; 19,95</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>15,48; 24,77</t>
+          <t>14,46; 22,74</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>16,9; 28,12</t>
+          <t>16,71; 28,17</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>22,83; 30,25</t>
+          <t>22,87; 30,76</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11,93; 19,08</t>
+          <t>11,7; 19,02</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>14,81; 22,01</t>
+          <t>14,12; 20,41</t>
         </is>
       </c>
     </row>
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3949</t>
+          <t>3716</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3949</t>
+          <t>3716</t>
         </is>
       </c>
     </row>
@@ -2068,17 +2068,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2381; 11398</t>
+          <t>2481; 11883</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7521; 19664</t>
+          <t>7436; 20103</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5204; 16554</t>
+          <t>5114; 17127</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2088,42 +2088,42 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5553</t>
+          <t>0; 5636</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4839; 14227</t>
+          <t>4828; 14002</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4927</t>
+          <t>0; 3898</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 11133</t>
+          <t>0; 11152</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4213; 15059</t>
+          <t>4240; 14851</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14970; 29962</t>
+          <t>14629; 30350</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5146; 18419</t>
+          <t>5252; 18183</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 14577</t>
+          <t>0; 13352</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7227</t>
+          <t>7104</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>1463</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8761</t>
+          <t>8567</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5960; 17280</t>
+          <t>6205; 17428</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12208; 28688</t>
+          <t>12241; 28728</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3985; 14479</t>
+          <t>3926; 13911</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1893; 15360</t>
+          <t>2265; 16224</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>983; 8363</t>
+          <t>969; 8243</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5893; 17511</t>
+          <t>6223; 17813</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2001; 10206</t>
+          <t>1116; 10209</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 5990</t>
+          <t>0; 7640</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9518; 22624</t>
+          <t>9016; 22403</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>21353; 41465</t>
+          <t>21500; 41043</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7560; 20562</t>
+          <t>7008; 20016</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3418; 17810</t>
+          <t>2844; 17630</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2480</t>
+          <t>2288</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3032</t>
+          <t>3059</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5513</t>
+          <t>5347</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1449; 9067</t>
+          <t>985; 8280</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7544; 20986</t>
+          <t>7106; 20174</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 9319</t>
+          <t>0; 8100</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 9352</t>
+          <t>0; 7092</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5683</t>
+          <t>0; 5264</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3729; 13892</t>
+          <t>3804; 13858</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>982; 8453</t>
+          <t>982; 8640</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1035; 6701</t>
+          <t>1112; 6792</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2777; 11681</t>
+          <t>2925; 12183</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13854; 29616</t>
+          <t>14402; 30775</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2818; 12510</t>
+          <t>2626; 13505</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2142; 10900</t>
+          <t>2114; 10682</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8720</t>
+          <t>8738</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>7835</t>
+          <t>8339</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>16554</t>
+          <t>17077</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2963; 11200</t>
+          <t>3012; 11681</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3830; 13406</t>
+          <t>3837; 13369</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>999; 8795</t>
+          <t>1069; 9445</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4392; 15701</t>
+          <t>4322; 15431</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>989; 7447</t>
+          <t>886; 6991</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3676; 14602</t>
+          <t>4263; 15111</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 5188</t>
+          <t>0; 5348</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4582; 12068</t>
+          <t>5087; 12942</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5099; 15801</t>
+          <t>5017; 15963</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10435; 25128</t>
+          <t>10128; 24562</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1951; 11427</t>
+          <t>1970; 10978</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10750; 23398</t>
+          <t>10953; 25076</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4156</t>
+          <t>4083</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3678</t>
+          <t>3849</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>7834</t>
+          <t>7932</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>826; 7040</t>
+          <t>881; 6936</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>968; 6276</t>
+          <t>976; 7296</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 6541</t>
+          <t>0; 6611</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1537; 8948</t>
+          <t>1457; 8693</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 3990</t>
+          <t>0; 3890</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6599; 19107</t>
+          <t>6678; 19083</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2080; 11095</t>
+          <t>2062; 11101</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1596; 7175</t>
+          <t>1582; 7492</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1716; 8895</t>
+          <t>1708; 8935</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8875; 22683</t>
+          <t>8468; 22486</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3270; 13535</t>
+          <t>3261; 14112</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4034; 13082</t>
+          <t>3939; 12727</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5059</t>
+          <t>5640</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>8605</t>
+          <t>9111</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>13664</t>
+          <t>14751</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 3844</t>
+          <t>0; 3775</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3818; 11912</t>
+          <t>3756; 11885</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 4006</t>
+          <t>0; 4008</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2437; 8712</t>
+          <t>2700; 9160</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>818; 6154</t>
+          <t>829; 5414</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3961; 13485</t>
+          <t>3954; 12764</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3159; 12601</t>
+          <t>3089; 12784</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5381; 12361</t>
+          <t>5828; 12858</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1679; 7466</t>
+          <t>881; 7461</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9986; 22641</t>
+          <t>10216; 22770</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3935; 13675</t>
+          <t>3979; 14769</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>8828; 18154</t>
+          <t>9993; 19847</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5429</t>
+          <t>6008</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>12954</t>
+          <t>13364</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>18383</t>
+          <t>19372</t>
         </is>
       </c>
     </row>
@@ -3321,57 +3321,57 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2666; 10485</t>
+          <t>2978; 11388</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1574; 7512</t>
+          <t>1547; 7392</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2788; 8594</t>
+          <t>3232; 9558</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 4589</t>
+          <t>0; 4956</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9593; 22017</t>
+          <t>8837; 22761</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1263; 10323</t>
+          <t>1249; 10505</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>9086; 17946</t>
+          <t>9217; 17944</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 5406</t>
+          <t>0; 5430</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>13924; 30015</t>
+          <t>13848; 30166</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3402; 14095</t>
+          <t>3309; 15106</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>13640; 24227</t>
+          <t>14569; 25477</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>33070</t>
+          <t>33861</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>41588</t>
+          <t>42901</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>74658</t>
+          <t>76762</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>22894; 42545</t>
+          <t>23046; 42555</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>56722; 87176</t>
+          <t>56671; 86248</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>22845; 44501</t>
+          <t>23303; 44783</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>23395; 46013</t>
+          <t>24518; 46864</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>9318; 23607</t>
+          <t>9943; 24120</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>56893; 87597</t>
+          <t>58345; 87992</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>18046; 38099</t>
+          <t>18150; 37960</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>33063; 52911</t>
+          <t>33584; 52788</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>36652; 60982</t>
+          <t>36241; 61094</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>122858; 162758</t>
+          <t>123051; 165548</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>46519; 74381</t>
+          <t>45605; 74175</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>61252; 91050</t>
+          <t>63985; 92485</t>
         </is>
       </c>
     </row>
